--- a/samples/packages_sample.xlsx
+++ b/samples/packages_sample.xlsx
@@ -1,41 +1,140 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AIS\TravelAI\samples\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6471CA9-58EA-4D55-BFD9-488C26910274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Packages" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+  <si>
+    <t>provider_id</t>
+  </si>
+  <si>
+    <t>provider_type</t>
+  </si>
+  <si>
+    <t>destination_name</t>
+  </si>
+  <si>
+    <t>package_name</t>
+  </si>
+  <si>
+    <t>package_type</t>
+  </si>
+  <si>
+    <t>travel_mode</t>
+  </si>
+  <si>
+    <t>summary</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>duration_days</t>
+  </si>
+  <si>
+    <t>duration_nights</t>
+  </si>
+  <si>
+    <t>base_price</t>
+  </si>
+  <si>
+    <t>currency_code</t>
+  </si>
+  <si>
+    <t>platform_service_fee_type</t>
+  </si>
+  <si>
+    <t>platform_service_fee_value</t>
+  </si>
+  <si>
+    <t>min_travelers</t>
+  </si>
+  <si>
+    <t>max_travelers</t>
+  </si>
+  <si>
+    <t>is_customizable</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>is_active</t>
+  </si>
+  <si>
+    <t>Agent</t>
+  </si>
+  <si>
+    <t>Queenstown</t>
+  </si>
+  <si>
+    <t>leisure</t>
+  </si>
+  <si>
+    <t>NZD</t>
+  </si>
+  <si>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Rotorua</t>
+  </si>
+  <si>
+    <t>family</t>
+  </si>
+  <si>
+    <t>car</t>
+  </si>
+  <si>
+    <t>Relax in mud pools</t>
+  </si>
+  <si>
+    <t>percentage</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>Queenstown City Tour Package</t>
+  </si>
+  <si>
+    <t>1-day city tour in Queenstown</t>
+  </si>
+  <si>
+    <t>City Tour and Gondola ride with hotel included</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotorua Thermal Splendour </t>
+  </si>
+  <si>
+    <t>Thermal springs family tour (Not included spa)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +164,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,110 +503,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="46.09765625" customWidth="1"/>
+    <col min="9" max="9" width="26.8984375" customWidth="1"/>
+    <col min="17" max="17" width="28.296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>provider_id</v>
-      </c>
-      <c r="B1" t="str">
-        <v>provider_type</v>
-      </c>
-      <c r="C1" t="str">
-        <v>destination_name</v>
-      </c>
-      <c r="D1" t="str">
-        <v>package_name</v>
-      </c>
-      <c r="E1" t="str">
-        <v>package_type</v>
-      </c>
-      <c r="F1" t="str">
-        <v>travel_mode</v>
-      </c>
-      <c r="G1" t="str">
-        <v>summary</v>
-      </c>
-      <c r="H1" t="str">
-        <v>description</v>
-      </c>
-      <c r="I1" t="str">
-        <v>duration_days</v>
-      </c>
-      <c r="J1" t="str">
-        <v>duration_nights</v>
-      </c>
-      <c r="K1" t="str">
-        <v>base_price</v>
-      </c>
-      <c r="L1" t="str">
-        <v>currency_code</v>
-      </c>
-      <c r="M1" t="str">
-        <v>platform_service_fee_type</v>
-      </c>
-      <c r="N1" t="str">
-        <v>platform_service_fee_value</v>
-      </c>
-      <c r="O1" t="str">
-        <v>min_travelers</v>
-      </c>
-      <c r="P1" t="str">
-        <v>max_travelers</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>is_customizable</v>
-      </c>
-      <c r="R1" t="str">
-        <v>status</v>
-      </c>
-      <c r="S1" t="str">
-        <v>is_active</v>
+    <row r="1" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>3</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Agent</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Queenstown</v>
-      </c>
-      <c r="D2" t="str">
-        <v>Queenstown Ski Explorer Package</v>
-      </c>
-      <c r="E2" t="str">
-        <v>leisure</v>
-      </c>
-      <c r="F2" t="str">
-        <v>flight</v>
-      </c>
-      <c r="G2" t="str">
-        <v>5-day adventure in Queenstown</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Skiing and Gondola ride with hotel included</v>
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" t="s">
+        <v>33</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>1500</v>
-      </c>
-      <c r="L2" t="str">
-        <v>NZD</v>
-      </c>
-      <c r="M2" t="str">
-        <v>fixed</v>
+        <v>300</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="O2">
         <v>1</v>
@@ -508,54 +621,54 @@
         <v>4</v>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="str">
-        <v>active</v>
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>24</v>
       </c>
       <c r="S2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Agent</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Rotorua</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Rotorua Thermal Splendour</v>
-      </c>
-      <c r="E3" t="str">
-        <v>family</v>
-      </c>
-      <c r="F3" t="str">
-        <v>car</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Relax in mud pools</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Thermal springs family tour and spa inclusions</v>
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>650</v>
-      </c>
-      <c r="L3" t="str">
-        <v>NZD</v>
-      </c>
-      <c r="M3" t="str">
-        <v>percentage</v>
+        <v>200</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
       </c>
       <c r="N3">
         <v>5</v>
@@ -569,16 +682,17 @@
       <c r="Q3" t="b">
         <v>0</v>
       </c>
-      <c r="R3" t="str">
-        <v>draft</v>
+      <c r="R3" t="s">
+        <v>30</v>
       </c>
       <c r="S3" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
+    <ignoredError sqref="A1:S1 B3:C3 B2:C2 E2 L2:M2 E3:G3 L3:S3 O2:P2 R2:S2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>